--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/FLORIDA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/FLORIDA_2022.xlsx
@@ -1057,7 +1057,7 @@
         <v>22</v>
       </c>
       <c r="D39">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="40">
@@ -1525,7 +1525,7 @@
         <v>22</v>
       </c>
       <c r="D65">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="66">
@@ -3055,7 +3055,7 @@
         <v>22</v>
       </c>
       <c r="D150">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="151">
@@ -3379,7 +3379,7 @@
         <v>22</v>
       </c>
       <c r="D168">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="169">
@@ -4837,7 +4837,7 @@
         <v>22</v>
       </c>
       <c r="D249">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="250">
@@ -5359,7 +5359,7 @@
         <v>22</v>
       </c>
       <c r="D278">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="279">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C326">
@@ -6259,7 +6259,7 @@
         <v>22</v>
       </c>
       <c r="D328">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="329">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C336">
@@ -7663,7 +7663,7 @@
         <v>23</v>
       </c>
       <c r="D406">
-        <v>0.0009972683519056497</v>
+        <v>0.0009972683519056495</v>
       </c>
     </row>
     <row r="407">
@@ -8635,7 +8635,7 @@
         <v>23</v>
       </c>
       <c r="D460">
-        <v>0.0009972683519056497</v>
+        <v>0.0009972683519056495</v>
       </c>
     </row>
     <row r="461">
@@ -12541,7 +12541,7 @@
         <v>23</v>
       </c>
       <c r="D677">
-        <v>0.0009972683519056497</v>
+        <v>0.0009972683519056495</v>
       </c>
     </row>
     <row r="678">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C752">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C754">
@@ -14575,7 +14575,7 @@
         <v>22</v>
       </c>
       <c r="D790">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="791">
@@ -14755,7 +14755,7 @@
         <v>23</v>
       </c>
       <c r="D800">
-        <v>0.0009972683519056497</v>
+        <v>0.0009972683519056495</v>
       </c>
     </row>
     <row r="801">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C880">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C881">
@@ -16663,7 +16663,7 @@
         <v>22</v>
       </c>
       <c r="D906">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="907">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C929">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C930">
@@ -17869,7 +17869,7 @@
         <v>22</v>
       </c>
       <c r="D973">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="974">
@@ -18499,7 +18499,7 @@
         <v>22</v>
       </c>
       <c r="D1008">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="1009">
@@ -19957,7 +19957,7 @@
         <v>23</v>
       </c>
       <c r="D1089">
-        <v>0.0009972683519056497</v>
+        <v>0.0009972683519056495</v>
       </c>
     </row>
     <row r="1090">
@@ -22315,7 +22315,7 @@
         <v>22</v>
       </c>
       <c r="D1220">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="1221">
@@ -23413,7 +23413,7 @@
         <v>22</v>
       </c>
       <c r="D1281">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="1282">
@@ -25278,7 +25278,7 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1385">
@@ -26059,7 +26059,7 @@
         <v>23</v>
       </c>
       <c r="D1428">
-        <v>0.0009972683519056497</v>
+        <v>0.0009972683519056495</v>
       </c>
     </row>
     <row r="1429">
@@ -26329,7 +26329,7 @@
         <v>23</v>
       </c>
       <c r="D1443">
-        <v>0.0009972683519056497</v>
+        <v>0.0009972683519056495</v>
       </c>
     </row>
     <row r="1444">
@@ -27229,7 +27229,7 @@
         <v>22</v>
       </c>
       <c r="D1493">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="1494">
@@ -27607,7 +27607,7 @@
         <v>22</v>
       </c>
       <c r="D1514">
-        <v>0.0009539088583445345</v>
+        <v>0.0009539088583445344</v>
       </c>
     </row>
     <row r="1515">
